--- a/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_Playoffs_Opponent_stats.xlsx
@@ -1616,19 +1616,19 @@
         <v>70</v>
       </c>
       <c r="J2" t="n">
-        <v>1196</v>
+        <v>1205</v>
       </c>
       <c r="K2" t="n">
-        <v>1211</v>
+        <v>1202</v>
       </c>
       <c r="L2" t="n">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="M2" t="n">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="N2" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O2" t="n">
         <v>2407</v>
@@ -1967,7 +1967,7 @@
         <v>492</v>
       </c>
       <c r="DW2" t="n">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="DX2" t="n">
         <v>25</v>
@@ -2111,16 +2111,16 @@
         <v>0.5443037974683544</v>
       </c>
       <c r="FS2" t="n">
-        <v>14.13235785953177</v>
+        <v>14.02680497925311</v>
       </c>
       <c r="FT2" t="n">
-        <v>14.58109000825764</v>
+        <v>14.69026622296173</v>
       </c>
       <c r="FU2" t="n">
-        <v>13.62717391304348</v>
+        <v>13.52539419087137</v>
       </c>
       <c r="FV2" t="n">
-        <v>13.82766308835673</v>
+        <v>13.93119800332779</v>
       </c>
       <c r="FW2" t="n">
         <v>0.3044747081712062</v>
@@ -2264,7 +2264,7 @@
         <v>25.26498740554156</v>
       </c>
       <c r="HR2" t="n">
-        <v>0.362876254180602</v>
+        <v>0.3676348547717843</v>
       </c>
       <c r="HS2" t="inlineStr"/>
       <c r="HT2" t="inlineStr"/>
@@ -2311,16 +2311,16 @@
         <v>27</v>
       </c>
       <c r="J3" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K3" t="n">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="L3" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M3" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N3" t="n">
         <v>80</v>
@@ -2646,7 +2646,7 @@
         <v>214</v>
       </c>
       <c r="DW3" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="DX3" t="n">
         <v>21</v>
@@ -2790,16 +2790,16 @@
         <v>0.4</v>
       </c>
       <c r="FS3" t="n">
-        <v>14.73242784380306</v>
+        <v>14.68257191201354</v>
       </c>
       <c r="FT3" t="n">
-        <v>14.40971524288107</v>
+        <v>14.4581512605042</v>
       </c>
       <c r="FU3" t="n">
-        <v>13.89388794567063</v>
+        <v>13.84686971235195</v>
       </c>
       <c r="FV3" t="n">
-        <v>13.87236180904523</v>
+        <v>13.91899159663866</v>
       </c>
       <c r="FW3" t="n">
         <v>0.3308550185873606</v>
@@ -2937,7 +2937,7 @@
         <v>25.77934782608695</v>
       </c>
       <c r="HR3" t="n">
-        <v>0.2835314091680815</v>
+        <v>0.2859560067681895</v>
       </c>
       <c r="HS3" t="n">
         <v>1</v>
@@ -2988,16 +2988,16 @@
         <v>105</v>
       </c>
       <c r="J4" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="K4" t="n">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="L4" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="M4" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N4" t="n">
         <v>78</v>
@@ -3335,7 +3335,7 @@
         <v>242</v>
       </c>
       <c r="DW4" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DX4" t="n">
         <v>13</v>
@@ -3477,16 +3477,16 @@
         <v>0.7241379310344828</v>
       </c>
       <c r="FS4" t="n">
-        <v>16.13623693379791</v>
+        <v>16.02456747404844</v>
       </c>
       <c r="FT4" t="n">
-        <v>13.82379310344828</v>
+        <v>13.91979166666667</v>
       </c>
       <c r="FU4" t="n">
-        <v>15.54303135888502</v>
+        <v>15.43546712802768</v>
       </c>
       <c r="FV4" t="n">
-        <v>13.28568965517241</v>
+        <v>13.37795138888889</v>
       </c>
       <c r="FW4" t="n">
         <v>0.3791748526522593</v>
@@ -3630,7 +3630,7 @@
         <v>25.10641711229946</v>
       </c>
       <c r="HR4" t="n">
-        <v>0.3344947735191638</v>
+        <v>0.3391003460207612</v>
       </c>
       <c r="HS4" t="n">
         <v>3</v>
@@ -3681,16 +3681,16 @@
         <v>49</v>
       </c>
       <c r="J5" t="n">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="K5" t="n">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="L5" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M5" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N5" t="n">
         <v>125</v>
@@ -4024,7 +4024,7 @@
         <v>273</v>
       </c>
       <c r="DW5" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="DX5" t="n">
         <v>20</v>
@@ -4166,16 +4166,16 @@
         <v>0.5106382978723404</v>
       </c>
       <c r="FS5" t="n">
-        <v>15.16447793326157</v>
+        <v>15.0994640943194</v>
       </c>
       <c r="FT5" t="n">
-        <v>15.97042553191489</v>
+        <v>16.03867521367522</v>
       </c>
       <c r="FU5" t="n">
-        <v>14.48719052744887</v>
+        <v>14.42508038585209</v>
       </c>
       <c r="FV5" t="n">
-        <v>15.31734042553192</v>
+        <v>15.38279914529915</v>
       </c>
       <c r="FW5" t="n">
         <v>0.2753792298716453</v>
@@ -4319,7 +4319,7 @@
         <v>25.62215568862275</v>
       </c>
       <c r="HR5" t="n">
-        <v>0.2604951560818084</v>
+        <v>0.2615219721329046</v>
       </c>
       <c r="HS5" t="n">
         <v>2</v>
@@ -4372,16 +4372,16 @@
         <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K6" t="n">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="L6" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M6" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N6" t="n">
         <v>96</v>
@@ -4715,7 +4715,7 @@
         <v>256</v>
       </c>
       <c r="DW6" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="DX6" t="n">
         <v>16</v>
@@ -4859,16 +4859,16 @@
         <v>0.4848484848484849</v>
       </c>
       <c r="FS6" t="n">
-        <v>15.57733918128655</v>
+        <v>15.50931586608442</v>
       </c>
       <c r="FT6" t="n">
-        <v>14.2515988372093</v>
+        <v>14.31401459854015</v>
       </c>
       <c r="FU6" t="n">
-        <v>14.76900584795322</v>
+        <v>14.70451237263464</v>
       </c>
       <c r="FV6" t="n">
-        <v>13.68037790697674</v>
+        <v>13.74029197080292</v>
       </c>
       <c r="FW6" t="n">
         <v>0.2722689075630252</v>
@@ -5012,7 +5012,7 @@
         <v>25.4029304029304</v>
       </c>
       <c r="HR6" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.3173216885007278</v>
       </c>
       <c r="HS6" t="n">
         <v>6</v>
@@ -5063,19 +5063,19 @@
         <v>55</v>
       </c>
       <c r="J7" t="n">
-        <v>1734</v>
+        <v>1738</v>
       </c>
       <c r="K7" t="n">
-        <v>1743</v>
+        <v>1739</v>
       </c>
       <c r="L7" t="n">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="M7" t="n">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="N7" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O7" t="n">
         <v>3477</v>
@@ -5412,7 +5412,7 @@
         <v>534</v>
       </c>
       <c r="DW7" t="n">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="DX7" t="n">
         <v>57</v>
@@ -5554,16 +5554,16 @@
         <v>0.4606741573033708</v>
       </c>
       <c r="FS7" t="n">
-        <v>15.20121107266436</v>
+        <v>15.1662255466053</v>
       </c>
       <c r="FT7" t="n">
-        <v>15.13545611015491</v>
+        <v>15.17027027027027</v>
       </c>
       <c r="FU7" t="n">
-        <v>14.47226066897347</v>
+        <v>14.43895281933257</v>
       </c>
       <c r="FV7" t="n">
-        <v>14.38313253012048</v>
+        <v>14.41621621621622</v>
       </c>
       <c r="FW7" t="n">
         <v>0.3128205128205128</v>
@@ -5707,7 +5707,7 @@
         <v>25.67450628366248</v>
       </c>
       <c r="HR7" t="n">
-        <v>0.2722029988465975</v>
+        <v>0.2738780207134637</v>
       </c>
       <c r="HS7" t="n">
         <v>6</v>
@@ -5760,19 +5760,19 @@
         <v>-283</v>
       </c>
       <c r="J8" t="n">
-        <v>1817</v>
+        <v>1823</v>
       </c>
       <c r="K8" t="n">
-        <v>1827</v>
+        <v>1821</v>
       </c>
       <c r="L8" t="n">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="M8" t="n">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="N8" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O8" t="n">
         <v>3644</v>
@@ -6111,7 +6111,7 @@
         <v>617</v>
       </c>
       <c r="DW8" t="n">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="DX8" t="n">
         <v>59</v>
@@ -6255,16 +6255,16 @@
         <v>0.5862068965517241</v>
       </c>
       <c r="FS8" t="n">
-        <v>14.33935057787562</v>
+        <v>14.29215578716402</v>
       </c>
       <c r="FT8" t="n">
-        <v>15.85407772304324</v>
+        <v>15.9063152114223</v>
       </c>
       <c r="FU8" t="n">
-        <v>13.78574573472757</v>
+        <v>13.74037301151947</v>
       </c>
       <c r="FV8" t="n">
-        <v>15.15703338806787</v>
+        <v>15.20697419000549</v>
       </c>
       <c r="FW8" t="n">
         <v>0.2922201138519924</v>
@@ -6408,7 +6408,7 @@
         <v>25.30128388017118</v>
       </c>
       <c r="HR8" t="n">
-        <v>0.3274628508530545</v>
+        <v>0.3296763576522216</v>
       </c>
       <c r="HS8" t="n">
         <v>5</v>
@@ -6461,16 +6461,16 @@
         <v>15</v>
       </c>
       <c r="J9" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="K9" t="n">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="L9" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="M9" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="N9" t="n">
         <v>66</v>
@@ -6802,7 +6802,7 @@
         <v>149</v>
       </c>
       <c r="DW9" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="DX9" t="n">
         <v>15</v>
@@ -6942,16 +6942,16 @@
         <v>0.5</v>
       </c>
       <c r="FS9" t="n">
-        <v>15.90503597122302</v>
+        <v>15.81967799642218</v>
       </c>
       <c r="FT9" t="n">
-        <v>15.57361853832442</v>
+        <v>15.65734767025089</v>
       </c>
       <c r="FU9" t="n">
-        <v>15.13741007194245</v>
+        <v>15.05617173524151</v>
       </c>
       <c r="FV9" t="n">
-        <v>14.8030303030303</v>
+        <v>14.8826164874552</v>
       </c>
       <c r="FW9" t="n">
         <v>0.262582056892779</v>
@@ -7095,7 +7095,7 @@
         <v>25.86862745098039</v>
       </c>
       <c r="HR9" t="n">
-        <v>0.2625899280575539</v>
+        <v>0.2665474060822898</v>
       </c>
       <c r="HS9" t="inlineStr"/>
       <c r="HT9" t="n">
@@ -7144,16 +7144,16 @@
         <v>-107</v>
       </c>
       <c r="J10" t="n">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="K10" t="n">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="L10" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="M10" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="N10" t="n">
         <v>192</v>
@@ -7495,7 +7495,7 @@
         <v>436</v>
       </c>
       <c r="DW10" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="DX10" t="n">
         <v>42</v>
@@ -7637,16 +7637,16 @@
         <v>0.4516129032258064</v>
       </c>
       <c r="FS10" t="n">
-        <v>15.0992439862543</v>
+        <v>15.0681755829904</v>
       </c>
       <c r="FT10" t="n">
-        <v>14.92180451127819</v>
+        <v>14.95246575342466</v>
       </c>
       <c r="FU10" t="n">
-        <v>14.46048109965636</v>
+        <v>14.43072702331962</v>
       </c>
       <c r="FV10" t="n">
-        <v>14.23732057416268</v>
+        <v>14.26657534246575</v>
       </c>
       <c r="FW10" t="n">
         <v>0.2879377431906615</v>
@@ -7790,7 +7790,7 @@
         <v>25.56062271062271</v>
       </c>
       <c r="HR10" t="n">
-        <v>0.2831615120274914</v>
+        <v>0.2846364883401921</v>
       </c>
       <c r="HS10" t="n">
         <v>3</v>
@@ -7841,16 +7841,16 @@
         <v>-23</v>
       </c>
       <c r="J11" t="n">
-        <v>1317</v>
+        <v>1324</v>
       </c>
       <c r="K11" t="n">
-        <v>1328</v>
+        <v>1321</v>
       </c>
       <c r="L11" t="n">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="M11" t="n">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="N11" t="n">
         <v>176</v>
@@ -8190,7 +8190,7 @@
         <v>484</v>
       </c>
       <c r="DW11" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="DX11" t="n">
         <v>40</v>
@@ -8334,16 +8334,16 @@
         <v>0.5357142857142857</v>
       </c>
       <c r="FS11" t="n">
-        <v>15.2665907365224</v>
+        <v>15.18587613293051</v>
       </c>
       <c r="FT11" t="n">
-        <v>15.44721385542169</v>
+        <v>15.52906888720666</v>
       </c>
       <c r="FU11" t="n">
-        <v>14.45299924069856</v>
+        <v>14.37658610271903</v>
       </c>
       <c r="FV11" t="n">
-        <v>14.61513554216868</v>
+        <v>14.69258137774414</v>
       </c>
       <c r="FW11" t="n">
         <v>0.2229020979020979</v>
@@ -8487,7 +8487,7 @@
         <v>25.95030927835051</v>
       </c>
       <c r="HR11" t="n">
-        <v>0.3386484434320425</v>
+        <v>0.3406344410876133</v>
       </c>
       <c r="HS11" t="n">
         <v>6</v>
@@ -8540,16 +8540,16 @@
         <v>-20</v>
       </c>
       <c r="J12" t="n">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="K12" t="n">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="L12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="M12" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="N12" t="n">
         <v>71</v>
@@ -8889,7 +8889,7 @@
         <v>105</v>
       </c>
       <c r="DW12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="DX12" t="n">
         <v>9</v>
@@ -9031,16 +9031,16 @@
         <v>0.5666666666666667</v>
       </c>
       <c r="FS12" t="n">
-        <v>15.35533230293663</v>
+        <v>15.26098310291859</v>
       </c>
       <c r="FT12" t="n">
-        <v>15.58704268292683</v>
+        <v>15.68266871165644</v>
       </c>
       <c r="FU12" t="n">
-        <v>14.77805255023184</v>
+        <v>14.68725038402458</v>
       </c>
       <c r="FV12" t="n">
-        <v>14.65487804878049</v>
+        <v>14.74478527607362</v>
       </c>
       <c r="FW12" t="n">
         <v>0.2428810720268007</v>
@@ -9184,7 +9184,7 @@
         <v>25.85</v>
       </c>
       <c r="HR12" t="n">
-        <v>0.1499227202472952</v>
+        <v>0.1536098310291859</v>
       </c>
       <c r="HS12" t="n">
         <v>1</v>
@@ -9235,16 +9235,16 @@
         <v>109</v>
       </c>
       <c r="J13" t="n">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="K13" t="n">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="L13" t="n">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="M13" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="N13" t="n">
         <v>136</v>
@@ -9582,7 +9582,7 @@
         <v>316</v>
       </c>
       <c r="DW13" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="DX13" t="n">
         <v>23</v>
@@ -9726,16 +9726,16 @@
         <v>0.5510204081632653</v>
       </c>
       <c r="FS13" t="n">
-        <v>15.66095423563778</v>
+        <v>15.58507751937984</v>
       </c>
       <c r="FT13" t="n">
-        <v>15.0397299903568</v>
+        <v>15.11259689922481</v>
       </c>
       <c r="FU13" t="n">
-        <v>14.80009737098345</v>
+        <v>14.72839147286822</v>
       </c>
       <c r="FV13" t="n">
-        <v>14.48158148505304</v>
+        <v>14.55174418604651</v>
       </c>
       <c r="FW13" t="n">
         <v>0.2431289640591966</v>
@@ -9879,7 +9879,7 @@
         <v>25.84442013129103</v>
       </c>
       <c r="HR13" t="n">
-        <v>0.2444011684518014</v>
+        <v>0.2470930232558139</v>
       </c>
       <c r="HS13" t="n">
         <v>3</v>
@@ -9932,19 +9932,19 @@
         <v>-173</v>
       </c>
       <c r="J14" t="n">
-        <v>2250</v>
+        <v>2262</v>
       </c>
       <c r="K14" t="n">
-        <v>2274</v>
+        <v>2262</v>
       </c>
       <c r="L14" t="n">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="M14" t="n">
-        <v>822</v>
+        <v>810</v>
       </c>
       <c r="N14" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O14" t="n">
         <v>4524</v>
@@ -10281,7 +10281,7 @@
         <v>676</v>
       </c>
       <c r="DW14" t="n">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="DX14" t="n">
         <v>55</v>
@@ -10425,16 +10425,16 @@
         <v>0.67</v>
       </c>
       <c r="FS14" t="n">
-        <v>15.32613333333333</v>
+        <v>15.2448275862069</v>
       </c>
       <c r="FT14" t="n">
-        <v>14.2287598944591</v>
+        <v>14.30424403183024</v>
       </c>
       <c r="FU14" t="n">
-        <v>14.55657777777778</v>
+        <v>14.47935455349249</v>
       </c>
       <c r="FV14" t="n">
-        <v>13.64872471416007</v>
+        <v>13.7211317418214</v>
       </c>
       <c r="FW14" t="n">
         <v>0.2803468208092486</v>
@@ -10578,7 +10578,7 @@
         <v>25.01705237515225</v>
       </c>
       <c r="HR14" t="n">
-        <v>0.2733333333333333</v>
+        <v>0.2767462422634837</v>
       </c>
       <c r="HS14" t="n">
         <v>8</v>
@@ -10631,16 +10631,16 @@
         <v>69</v>
       </c>
       <c r="J15" t="n">
+        <v>384</v>
+      </c>
+      <c r="K15" t="n">
         <v>383</v>
       </c>
-      <c r="K15" t="n">
-        <v>384</v>
-      </c>
       <c r="L15" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M15" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N15" t="n">
         <v>53</v>
@@ -10968,7 +10968,7 @@
         <v>169</v>
       </c>
       <c r="DW15" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="DX15" t="n">
         <v>10</v>
@@ -11108,16 +11108,16 @@
         <v>0.6086956521739131</v>
       </c>
       <c r="FS15" t="n">
-        <v>15.20835509138381</v>
+        <v>15.16875</v>
       </c>
       <c r="FT15" t="n">
-        <v>14.83125</v>
+        <v>14.86997389033943</v>
       </c>
       <c r="FU15" t="n">
-        <v>14.48355091383812</v>
+        <v>14.44583333333333</v>
       </c>
       <c r="FV15" t="n">
-        <v>14.0046875</v>
+        <v>14.04125326370757</v>
       </c>
       <c r="FW15" t="n">
         <v>0.2138888888888889</v>
@@ -11255,7 +11255,7 @@
         <v>25.44585987261146</v>
       </c>
       <c r="HR15" t="n">
-        <v>0.3550913838120104</v>
+        <v>0.3567708333333333</v>
       </c>
       <c r="HS15" t="inlineStr"/>
       <c r="HT15" t="inlineStr"/>
@@ -11304,16 +11304,16 @@
         <v>33</v>
       </c>
       <c r="J16" t="n">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="K16" t="n">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="L16" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M16" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N16" t="n">
         <v>93</v>
@@ -11651,7 +11651,7 @@
         <v>239</v>
       </c>
       <c r="DW16" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="DX16" t="n">
         <v>20</v>
@@ -11793,16 +11793,16 @@
         <v>0.5606060606060606</v>
       </c>
       <c r="FS16" t="n">
-        <v>15.27606060606061</v>
+        <v>15.25295007564297</v>
       </c>
       <c r="FT16" t="n">
-        <v>15.13183183183183</v>
+        <v>15.15458646616541</v>
       </c>
       <c r="FU16" t="n">
-        <v>14.45727272727273</v>
+        <v>14.43540090771558</v>
       </c>
       <c r="FV16" t="n">
-        <v>14.33153153153153</v>
+        <v>14.35308270676692</v>
       </c>
       <c r="FW16" t="n">
         <v>0.2517482517482518</v>
@@ -11946,7 +11946,7 @@
         <v>25.61394230769231</v>
       </c>
       <c r="HR16" t="n">
-        <v>0.3515151515151515</v>
+        <v>0.3524962178517398</v>
       </c>
       <c r="HS16" t="n">
         <v>5</v>
